--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -524,22 +524,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>158.1199951171875</v>
+        <v>153.6799926757812</v>
       </c>
       <c r="I2" t="n">
-        <v>64.16509401855468</v>
+        <v>62.36334102783203</v>
       </c>
       <c r="J2" t="n">
         <v>63.180012</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9850820185546851</v>
+        <v>-0.8166709721679695</v>
       </c>
       <c r="L2" t="n">
-        <v>1.559167191286202</v>
+        <v>-1.292609713603678</v>
       </c>
       <c r="M2" t="n">
-        <v>5.995861589335957</v>
+        <v>5.863276186867509</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>54.89197868867951</v>
+        <v>55.2289898790773</v>
       </c>
     </row>
     <row r="4">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.165908813476562</v>
+        <v>1.152737736701965</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>418.5612640380859</v>
+        <v>413.8328474760056</v>
       </c>
       <c r="J4" t="n">
-        <v>418.5612640380859</v>
+        <v>413.8328474760056</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>39.11215972198453</v>
+        <v>38.90773393405521</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -524,22 +524,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>153.6799926757812</v>
+        <v>154.2799987792969</v>
       </c>
       <c r="I2" t="n">
-        <v>62.36334102783203</v>
+        <v>62.60682350463867</v>
       </c>
       <c r="J2" t="n">
         <v>63.180012</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8166709721679695</v>
+        <v>-0.5731884953613289</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.292609713603678</v>
+        <v>-0.9072307478531801</v>
       </c>
       <c r="M2" t="n">
-        <v>5.863276186867509</v>
+        <v>5.881387156502644</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>55.2289898790773</v>
+        <v>55.18413271819112</v>
       </c>
     </row>
     <row r="4">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.152737736701965</v>
+        <v>1.154467821121216</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>413.8328474760056</v>
+        <v>414.4539477825165</v>
       </c>
       <c r="J4" t="n">
-        <v>413.8328474760056</v>
+        <v>414.4539477825165</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>38.90773393405521</v>
+        <v>38.93448012530624</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -524,22 +524,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>154.2799987792969</v>
+        <v>154.2899932861328</v>
       </c>
       <c r="I2" t="n">
-        <v>62.60682350463867</v>
+        <v>62.61087927551269</v>
       </c>
       <c r="J2" t="n">
         <v>63.180012</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5731884953613289</v>
+        <v>-0.5691327244873037</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.9072307478531801</v>
+        <v>-0.9008113586418814</v>
       </c>
       <c r="M2" t="n">
-        <v>5.881387156502644</v>
+        <v>5.881745752447848</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>55.18413271819112</v>
+        <v>55.18392246428241</v>
       </c>
     </row>
     <row r="4">
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>38.93448012530624</v>
+        <v>38.93433178326974</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -539,7 +539,7 @@
         <v>-0.9008113586418814</v>
       </c>
       <c r="M2" t="n">
-        <v>5.881745752447848</v>
+        <v>5.881481396233408</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>55.18392246428241</v>
+        <v>55.1814422120827</v>
       </c>
     </row>
     <row r="4">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.154467821121216</v>
+        <v>1.154601097106934</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>414.4539477825165</v>
+        <v>414.5017938613892</v>
       </c>
       <c r="J4" t="n">
-        <v>414.4539477825165</v>
+        <v>414.5017938613892</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>38.93433178326974</v>
+        <v>38.93707639168388</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -524,22 +524,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>154.2899932861328</v>
+        <v>154.3000030517578</v>
       </c>
       <c r="I2" t="n">
-        <v>62.61087927551269</v>
+        <v>62.61494123840332</v>
       </c>
       <c r="J2" t="n">
         <v>63.180012</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5691327244873037</v>
+        <v>-0.5650707615966795</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.9008113586418814</v>
+        <v>-0.8943821688363711</v>
       </c>
       <c r="M2" t="n">
-        <v>5.881481396233408</v>
+        <v>5.881576174197621</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>55.1814422120827</v>
+        <v>55.17875164737616</v>
       </c>
     </row>
     <row r="4">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.154601097106934</v>
+        <v>1.154734373092651</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>414.5017938613892</v>
+        <v>414.5496399402618</v>
       </c>
       <c r="J4" t="n">
-        <v>414.5017938613892</v>
+        <v>414.5496399402618</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>38.93707639168388</v>
+        <v>38.93967217842623</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -539,7 +539,7 @@
         <v>-0.8943821688363711</v>
       </c>
       <c r="M2" t="n">
-        <v>5.881576174197621</v>
+        <v>5.881311613958689</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>55.17875164737616</v>
+        <v>55.17626964199403</v>
       </c>
     </row>
     <row r="4">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.154734373092651</v>
+        <v>1.154867768287659</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>414.5496399402618</v>
+        <v>414.5975288152695</v>
       </c>
       <c r="J4" t="n">
-        <v>414.5496399402618</v>
+        <v>414.5975288152695</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>38.93967217842623</v>
+        <v>38.94241874404729</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -524,22 +524,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>154.3000030517578</v>
+        <v>156.2899932861328</v>
       </c>
       <c r="I2" t="n">
-        <v>62.61494123840332</v>
+        <v>63.42247927551269</v>
       </c>
       <c r="J2" t="n">
         <v>63.180012</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5650707615966795</v>
+        <v>0.2424672755126949</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.8943821688363711</v>
+        <v>0.3837721264008226</v>
       </c>
       <c r="M2" t="n">
-        <v>5.881311613958689</v>
+        <v>5.947825733650836</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>55.17626964199403</v>
+        <v>55.08979325044315</v>
       </c>
     </row>
     <row r="4">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.154867768287659</v>
+        <v>1.157273530960083</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>414.5975288152695</v>
+        <v>415.4611976146698</v>
       </c>
       <c r="J4" t="n">
-        <v>414.5975288152695</v>
+        <v>415.4611976146698</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>38.94241874404729</v>
+        <v>38.96238101590601</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -524,22 +524,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>156.2899932861328</v>
+        <v>157.5599975585938</v>
       </c>
       <c r="I2" t="n">
-        <v>63.42247927551269</v>
+        <v>63.93784700927734</v>
       </c>
       <c r="J2" t="n">
         <v>63.180012</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2424672755126949</v>
+        <v>0.7578350092773434</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3837721264008226</v>
+        <v>1.199485383569322</v>
       </c>
       <c r="M2" t="n">
-        <v>5.947825733650836</v>
+        <v>6.02194554590509</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>55.08979325044315</v>
+        <v>55.32672176962327</v>
       </c>
     </row>
     <row r="4">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.157273530960083</v>
+        <v>1.143118381500244</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>415.4611976146698</v>
+        <v>410.3794989585876</v>
       </c>
       <c r="J4" t="n">
-        <v>415.4611976146698</v>
+        <v>410.3794989585876</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>38.96238101590601</v>
+        <v>38.65133268447165</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -539,7 +539,7 @@
         <v>1.199485383569322</v>
       </c>
       <c r="M2" t="n">
-        <v>6.02194554590509</v>
+        <v>6.021679284871804</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>55.32672176962327</v>
+        <v>55.32427549208815</v>
       </c>
     </row>
     <row r="4">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.143118381500244</v>
+        <v>1.143249154090881</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>410.3794989585876</v>
+        <v>410.4264463186264</v>
       </c>
       <c r="J4" t="n">
-        <v>410.3794989585876</v>
+        <v>410.4264463186264</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>38.65133268447165</v>
+        <v>38.65404522304005</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -524,22 +524,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>157.5599975585938</v>
+        <v>157.8099975585938</v>
       </c>
       <c r="I2" t="n">
-        <v>63.93784700927734</v>
+        <v>64.03929700927735</v>
       </c>
       <c r="J2" t="n">
         <v>63.180012</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7578350092773434</v>
+        <v>0.8592850092773503</v>
       </c>
       <c r="L2" t="n">
-        <v>1.199485383569322</v>
+        <v>1.360058319199671</v>
       </c>
       <c r="M2" t="n">
-        <v>6.021679284871804</v>
+        <v>6.028257815428275</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>55.32427549208815</v>
+        <v>55.29697629260393</v>
       </c>
     </row>
     <row r="4">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.143249154090881</v>
+        <v>1.144426703453064</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>410.4264463186264</v>
+        <v>410.84918653965</v>
       </c>
       <c r="J4" t="n">
-        <v>410.4264463186264</v>
+        <v>410.84918653965</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>38.65404522304005</v>
+        <v>38.67476589196778</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -524,22 +524,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>157.8099975585938</v>
+        <v>157.6300048828125</v>
       </c>
       <c r="I2" t="n">
-        <v>64.03929700927735</v>
+        <v>63.96625598144531</v>
       </c>
       <c r="J2" t="n">
         <v>63.180012</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8592850092773503</v>
+        <v>0.7862439814453168</v>
       </c>
       <c r="L2" t="n">
-        <v>1.360058319199671</v>
+        <v>1.244450509831047</v>
       </c>
       <c r="M2" t="n">
-        <v>6.028257815428275</v>
+        <v>6.026854003461519</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>55.29697629260393</v>
+        <v>55.34722632946269</v>
       </c>
     </row>
     <row r="4">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.144426703453064</v>
+        <v>1.141943573951721</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>410.84918653965</v>
+        <v>409.9577430486679</v>
       </c>
       <c r="J4" t="n">
-        <v>410.84918653965</v>
+        <v>409.9577430486679</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>38.67476589196778</v>
+        <v>38.62591966707578</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -524,22 +524,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>157.6300048828125</v>
+        <v>154.7799987792969</v>
       </c>
       <c r="I2" t="n">
-        <v>63.96625598144531</v>
+        <v>62.80972350463867</v>
       </c>
       <c r="J2" t="n">
         <v>63.180012</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7862439814453168</v>
+        <v>-0.3702884953613292</v>
       </c>
       <c r="L2" t="n">
-        <v>1.244450509831047</v>
+        <v>-0.5860848765925041</v>
       </c>
       <c r="M2" t="n">
-        <v>6.026854003461519</v>
+        <v>5.921986154349225</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>55.34722632946269</v>
+        <v>55.38556982172433</v>
       </c>
     </row>
     <row r="4">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.141943573951721</v>
+        <v>1.143118381500244</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>409.9577430486679</v>
+        <v>410.3794989585876</v>
       </c>
       <c r="J4" t="n">
-        <v>409.9577430486679</v>
+        <v>410.3794989585876</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>38.62591966707578</v>
+        <v>38.69244402392643</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -524,22 +524,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>154.7799987792969</v>
+        <v>152.2200012207031</v>
       </c>
       <c r="I2" t="n">
-        <v>62.80972350463867</v>
+        <v>61.77087649536133</v>
       </c>
       <c r="J2" t="n">
         <v>63.180012</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3702884953613292</v>
+        <v>-1.40913550463867</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5860848765925041</v>
+        <v>-2.230350169352088</v>
       </c>
       <c r="M2" t="n">
-        <v>5.921986154349225</v>
+        <v>5.821730340084267</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>55.38556982172433</v>
+        <v>55.36361547229324</v>
       </c>
     </row>
     <row r="4">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.143118381500244</v>
+        <v>1.147183656692505</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>410.3794989585876</v>
+        <v>411.8389327526093</v>
       </c>
       <c r="J4" t="n">
-        <v>410.3794989585876</v>
+        <v>411.8389327526093</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>38.69244402392643</v>
+        <v>38.81465418762251</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -524,22 +524,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>152.2200012207031</v>
+        <v>159.9199981689453</v>
       </c>
       <c r="I2" t="n">
-        <v>61.77087649536133</v>
+        <v>64.89553525695801</v>
       </c>
       <c r="J2" t="n">
         <v>63.180012</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.40913550463867</v>
+        <v>1.715523256958015</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.230350169352088</v>
+        <v>2.715294287943495</v>
       </c>
       <c r="M2" t="n">
-        <v>5.821730340084267</v>
+        <v>6.087129355785146</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>55.36361547229324</v>
+        <v>55.10028360672901</v>
       </c>
     </row>
     <row r="4">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.147183656692505</v>
+        <v>1.152604818344116</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>411.8389327526093</v>
+        <v>413.7851297855377</v>
       </c>
       <c r="J4" t="n">
-        <v>411.8389327526093</v>
+        <v>413.7851297855377</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>38.81465418762251</v>
+        <v>38.81258703748583</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -524,22 +524,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>159.9199981689453</v>
+        <v>162.25</v>
       </c>
       <c r="I2" t="n">
-        <v>64.89553525695801</v>
+        <v>65.84105</v>
       </c>
       <c r="J2" t="n">
         <v>63.180012</v>
       </c>
       <c r="K2" t="n">
-        <v>1.715523256958015</v>
+        <v>2.661037999999998</v>
       </c>
       <c r="L2" t="n">
-        <v>2.715294287943495</v>
+        <v>4.21183522408954</v>
       </c>
       <c r="M2" t="n">
-        <v>6.087129355785146</v>
+        <v>6.160668413155146</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>55.10028360672901</v>
+        <v>54.96512352004908</v>
       </c>
     </row>
     <row r="4">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.152604818344116</v>
+        <v>1.157273530960083</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>413.7851297855377</v>
+        <v>415.4611976146698</v>
       </c>
       <c r="J4" t="n">
-        <v>413.7851297855377</v>
+        <v>415.4611976146698</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>38.81258703748583</v>
+        <v>38.87420806679579</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -524,22 +524,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>162.25</v>
+        <v>160.0599975585938</v>
       </c>
       <c r="I2" t="n">
-        <v>65.84105</v>
+        <v>64.95234700927735</v>
       </c>
       <c r="J2" t="n">
         <v>63.180012</v>
       </c>
       <c r="K2" t="n">
-        <v>2.661037999999998</v>
+        <v>1.772335009277349</v>
       </c>
       <c r="L2" t="n">
-        <v>4.21183522408954</v>
+        <v>2.805214739872713</v>
       </c>
       <c r="M2" t="n">
-        <v>6.160668413155146</v>
+        <v>6.08174984555891</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>54.96512352004908</v>
+        <v>55.00343676982734</v>
       </c>
     </row>
     <row r="4">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.157273530960083</v>
+        <v>1.157675385475159</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>415.4611976146698</v>
+        <v>415.605463385582</v>
       </c>
       <c r="J4" t="n">
-        <v>415.4611976146698</v>
+        <v>415.605463385582</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>38.87420806679579</v>
+        <v>38.91481338461374</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,69 +524,69 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>160.0599975585938</v>
+        <v>160.7149963378906</v>
       </c>
       <c r="I2" t="n">
-        <v>64.95234700927735</v>
+        <v>65.21814551391601</v>
       </c>
       <c r="J2" t="n">
         <v>63.180012</v>
       </c>
       <c r="K2" t="n">
-        <v>1.772335009277349</v>
+        <v>2.038133513916016</v>
       </c>
       <c r="L2" t="n">
-        <v>2.805214739872713</v>
+        <v>3.225915047176654</v>
       </c>
       <c r="M2" t="n">
-        <v>6.08174984555891</v>
+        <v>6.11641010044574</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2.8146</v>
+      </c>
+      <c r="D3" t="n">
+        <v>160.58</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>587.4299999999999</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>160.7149963378906</v>
       </c>
       <c r="I3" t="n">
-        <v>587.4299999999999</v>
+        <v>452.348428692627</v>
       </c>
       <c r="J3" t="n">
-        <v>587.4299999999999</v>
+        <v>452.958468</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0.6100393073730856</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.1346788614123195</v>
       </c>
       <c r="M3" t="n">
-        <v>55.00343676982734</v>
+        <v>42.42298636942972</v>
       </c>
     </row>
     <row r="4">
@@ -597,11 +597,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>359</v>
+        <v>0.01</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -611,20 +611,20 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.157675385475159</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>415.605463385582</v>
+        <v>0.01</v>
       </c>
       <c r="J4" t="n">
-        <v>415.605463385582</v>
+        <v>0.01</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +633,148 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>38.91481338461374</v>
+        <v>0.0009378387030555234</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1.167814970016479</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.017283496856689</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.017283496856689</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3767563944498435</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="D6" t="n">
+        <v>708.215297</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>707.2100219726562</v>
+      </c>
+      <c r="I6" t="n">
+        <v>224.6806239807129</v>
+      </c>
+      <c r="J6" t="n">
+        <v>225.9899998569</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1.309375876187119</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.5793954940555925</v>
+      </c>
+      <c r="M6" t="n">
+        <v>21.07141849957775</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SGOV</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3.1813</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100.5878</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>100.5899963378906</v>
+      </c>
+      <c r="I7" t="n">
+        <v>320.0069553497314</v>
+      </c>
+      <c r="J7" t="n">
+        <v>320.98996814</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.9830127902685604</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.3062440848119649</v>
+      </c>
+      <c r="M7" t="n">
+        <v>30.01149079739389</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4058</v>
+        <v>3.2204</v>
       </c>
       <c r="D2" t="n">
-        <v>154.14</v>
+        <v>159.77</v>
       </c>
       <c r="E2" t="n">
-        <v>0.63</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,43 +524,43 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>160.7149963378906</v>
+        <v>161.5700073242188</v>
       </c>
       <c r="I2" t="n">
-        <v>65.21814551391601</v>
+        <v>520.3200515869141</v>
       </c>
       <c r="J2" t="n">
-        <v>63.180012</v>
+        <v>515.4633080000001</v>
       </c>
       <c r="K2" t="n">
-        <v>2.038133513916016</v>
+        <v>4.856743586914035</v>
       </c>
       <c r="L2" t="n">
-        <v>3.225915047176654</v>
+        <v>0.9422093700050584</v>
       </c>
       <c r="M2" t="n">
-        <v>6.11641010044574</v>
+        <v>48.63942491000949</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.8146</v>
+        <v>4.03</v>
       </c>
       <c r="D3" t="n">
-        <v>160.58</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -571,43 +571,43 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>160.7149963378906</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>452.348428692627</v>
+        <v>4.03</v>
       </c>
       <c r="J3" t="n">
-        <v>452.958468</v>
+        <v>4.03</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6100393073730856</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1346788614123195</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>42.42298636942972</v>
+        <v>0.3767236757251813</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>VOO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.01</v>
+        <v>0.3177</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>708.215297</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -618,163 +618,69 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>708.75</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01</v>
+        <v>225.169875</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01</v>
+        <v>225.9899998569</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-0.8201248569000086</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.3629031627148648</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0009378387030555234</v>
+        <v>21.04883944729022</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>SGOV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.44</v>
+        <v>3.1813</v>
       </c>
       <c r="D5" t="n">
+        <v>100.5878</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1.167814970016479</v>
-      </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>100.6600036621094</v>
       </c>
       <c r="I5" t="n">
-        <v>4.017283496856689</v>
+        <v>320.2296696502685</v>
       </c>
       <c r="J5" t="n">
-        <v>4.017283496856689</v>
+        <v>320.98996814</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0.76029848973144</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.2368605144070532</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3767563944498435</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ETF</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>VOO</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.3177</v>
-      </c>
-      <c r="D6" t="n">
-        <v>708.215297</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>707.2100219726562</v>
-      </c>
-      <c r="I6" t="n">
-        <v>224.6806239807129</v>
-      </c>
-      <c r="J6" t="n">
-        <v>225.9899998569</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-1.309375876187119</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-0.5793954940555925</v>
-      </c>
-      <c r="M6" t="n">
-        <v>21.07141849957775</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ETF</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SGOV</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>3.1813</v>
-      </c>
-      <c r="D7" t="n">
-        <v>100.5878</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>100.5899963378906</v>
-      </c>
-      <c r="I7" t="n">
-        <v>320.0069553497314</v>
-      </c>
-      <c r="J7" t="n">
-        <v>320.98996814</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.9830127902685604</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-0.3062440848119649</v>
-      </c>
-      <c r="M7" t="n">
-        <v>30.01149079739389</v>
+        <v>29.93501196697511</v>
       </c>
     </row>
   </sheetData>

--- a/Data/df.xlsx
+++ b/Data/df.xlsx
@@ -524,22 +524,22 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>161.5700073242188</v>
+        <v>159.3099975585938</v>
       </c>
       <c r="I2" t="n">
-        <v>520.3200515869141</v>
+        <v>513.0419161376954</v>
       </c>
       <c r="J2" t="n">
         <v>515.4633080000001</v>
       </c>
       <c r="K2" t="n">
-        <v>4.856743586914035</v>
+        <v>-2.421391862304745</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9422093700050584</v>
+        <v>-0.4697505767577824</v>
       </c>
       <c r="M2" t="n">
-        <v>48.63942491000949</v>
+        <v>48.44656030086954</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3767236757251813</v>
+        <v>0.380552995518019</v>
       </c>
     </row>
     <row r="4">
@@ -618,22 +618,22 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>708.75</v>
+        <v>700.280029296875</v>
       </c>
       <c r="I4" t="n">
-        <v>225.169875</v>
+        <v>222.4789653076172</v>
       </c>
       <c r="J4" t="n">
         <v>225.9899998569</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8201248569000086</v>
+        <v>-3.511034549282812</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3629031627148648</v>
+        <v>-1.553623855704256</v>
       </c>
       <c r="M4" t="n">
-        <v>21.04883944729022</v>
+        <v>21.00869396713726</v>
       </c>
     </row>
     <row r="5">
@@ -665,22 +665,22 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>100.6600036621094</v>
+        <v>100.4100036621094</v>
       </c>
       <c r="I5" t="n">
-        <v>320.2296696502685</v>
+        <v>319.4343446502685</v>
       </c>
       <c r="J5" t="n">
         <v>320.98996814</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.76029848973144</v>
+        <v>-1.555623489731431</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2368605144070532</v>
+        <v>-0.4846330552775858</v>
       </c>
       <c r="M5" t="n">
-        <v>29.93501196697511</v>
+        <v>30.16419273647518</v>
       </c>
     </row>
   </sheetData>
